--- a/tables/research_log.xlsx
+++ b/tables/research_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20369"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andy\OneDrive - University College London\SCUA\CASA_thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choic\CASA\london-cooling-access-equity-thesis\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CB3B05-418F-43E9-95C6-FED268DDCA54}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC3F807-8199-4006-8EB2-3DDD5014CA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7485" xr2:uid="{2919A5B8-BF7C-4943-B2AE-9E8EB0A96388}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{2919A5B8-BF7C-4943-B2AE-9E8EB0A96388}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Date</t>
   </si>
@@ -33,29 +33,111 @@
     <t>Task</t>
   </si>
   <si>
-    <t>31st May 2020</t>
-  </si>
-  <si>
-    <t>7th June 2020</t>
-  </si>
-  <si>
-    <t>data search, commenced literature review</t>
-  </si>
-  <si>
-    <t>revised literature in the direction of x</t>
+    <t>Completed Ethics form and sent to supervisor for approval.</t>
+  </si>
+  <si>
+    <t>Gather data sources and shortlisted potential study areas, ethics form approved by supervisor and submitted.</t>
+  </si>
+  <si>
+    <t>Setup a GitHub repository for data preparation and pre-validation purpose.</t>
+  </si>
+  <si>
+    <t>Data pre-validation for satellite imagery for shortlisted study areas via Google Earth Engine completed, confirmed study area, downloaded r5r required data files and converted data into GTFS format.</t>
+  </si>
+  <si>
+    <t>Data pre-validation resumed, noticed missing data problems with the converted GTFS data, found an alternative dataset (as supported by literature).</t>
+  </si>
+  <si>
+    <t>Finalised research questions and objectives and started drafting introduction.</t>
+  </si>
+  <si>
+    <t>Finished first draft introduction, start literature review.</t>
+  </si>
+  <si>
+    <t>Worked on minor refinements suggestions for introduction chapter.</t>
+  </si>
+  <si>
+    <t>Meeting with supervisor, revised cleaner objectives, discussed literature review outline, updated supervisor on changes in choice of data sources and potential approaches in methodology.</t>
+  </si>
+  <si>
+    <t>First section of literature review complete, start second section of literature review and continue exploring on methodologies.</t>
+  </si>
+  <si>
+    <t>Meeting with supervisor, discussed some minor methodology uncertainties and finer details of methodology approach with supervisor.</t>
+  </si>
+  <si>
+    <t>Continue working on literature review, started retrieving data on Google Earth Engine</t>
+  </si>
+  <si>
+    <t>Revised early sections of literature review and continue other sections of literature review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review methodological approaches in existing literature for informing methodology for this study  </t>
+  </si>
+  <si>
+    <t>Completed first full draft for literature review, proceeded on to methodology.</t>
+  </si>
+  <si>
+    <t>Setup a GitHub repository and R project for analysis and submission.</t>
+  </si>
+  <si>
+    <t>Completed remote sensing analysis (Stage 1), updated Google Earth Engine scripts to GitHub repository.</t>
+  </si>
+  <si>
+    <t>Encountered data ambiguities in running r5r travel time matrices, where origin (from_id) and destination values (to_id) reversed (for Walking and Cycling modes) under the whole Greater London computation using package version 2.3.0. Identified problem to be raised from versions issues, updated and re-computed travel time matrices.</t>
+  </si>
+  <si>
+    <t>Completed analysis (Stage 2 and 3) and edited initial figures and outputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting with supervisor, discussed some uncertainties in the final step of methodology and shared initial results and figure outputs. </t>
+  </si>
+  <si>
+    <t>Wrapped up methodology section and proceed to writing results and discussion.</t>
+  </si>
+  <si>
+    <t>Edited format as required according to the dissertation handbook, draft sent to supervisor.</t>
+  </si>
+  <si>
+    <t>Final sections and figures completed.</t>
+  </si>
+  <si>
+    <t>Revise draft.</t>
+  </si>
+  <si>
+    <t>Meeting with supervisor, clarification of any final questions on final draft.</t>
+  </si>
+  <si>
+    <t>Tidy GitHub repository for submission.</t>
+  </si>
+  <si>
+    <t>Final edits.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,7 +148,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -74,12 +156,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -98,9 +221,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -138,7 +261,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -244,7 +367,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -386,7 +509,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -394,35 +517,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0918B5B-C1DF-4991-A3CC-9E87313077B4}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="105.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="4">
+        <v>46121</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:2" ht="210" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="171" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="197.25" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="4">
+        <v>46170</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="118.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="131.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="4">
+        <v>46182</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="92.25" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="92.25" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="4">
+        <v>46185</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="105.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="4">
+        <v>46201</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="105.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="4">
+        <v>46205</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="302.25" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="6">
+        <v>46210</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="4">
+        <v>46221</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="131.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="92.25" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="6">
+        <v>46237</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="4">
+        <v>46246</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="4">
+        <v>46252</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="6">
+        <v>46263</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
